--- a/History/Backup Dictionaries_Task_Happs.xlsx
+++ b/History/Backup Dictionaries_Task_Happs.xlsx
@@ -430,10 +430,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A2:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
@@ -12245,7 +12244,9 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1"/>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>